--- a/artfynd/A 41784-2024 artfynd.xlsx
+++ b/artfynd/A 41784-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117614189</v>
+        <v>117614180</v>
       </c>
       <c r="B2" t="n">
-        <v>97838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608159</v>
+        <v>607881</v>
       </c>
       <c r="R2" t="n">
-        <v>6955254</v>
+        <v>6955204</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>117614188</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>117614189</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lycke, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608159</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6955254</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41784-2024 artfynd.xlsx
+++ b/artfynd/A 41784-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614180</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614188</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614189</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>